--- a/aq_files/0361.xlsx
+++ b/aq_files/0361.xlsx
@@ -1,195 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
-  <si>
-    <t>Comparison_ID,Aspect,Spark_SQL_Value,Hive_Value,Spark_SQL_Description,Hive_Description,Performance_Difference,Use_Case_Winner,Key_Insight</t>
-  </si>
-  <si>
-    <t>CMP-001,Execution_Engine,In-memory (Spark Core),MapReduce (Tez/Spark optional),Uses in-memory processing with DAG execution,Uses disk-based MapReduce (can use Tez for DAG),Spark 10-100x faster for iterative jobs,Spark SQL,Spark's in-memory execution provides massive speed advantage</t>
-  </si>
-  <si>
-    <t>CMP-002,Query_Latency,Sub-second to minutes,Minutes to hours,Optimized for low-latency interactive queries,Batch-oriented with higher latency,Spark 10-50x faster,Spark SQL,Spark SQL is optimized for interactive analytics</t>
-  </si>
-  <si>
-    <t>CMP-003,Data_Processing_Speed,100-500 MB/s per core,10-50 MB/s per core,In-memory processing with code generation,Disk-based processing with serialization,Spark 5-10x faster,Spark SQL,Spark's code generation and in-memory processing are significantly faster</t>
-  </si>
-  <si>
-    <t>CMP-004,Startup_Time,5-30 seconds,2-10 seconds,Spark context initialization overhead,Container startup overhead,Spark slower for short jobs,Hive for short jobs,Spark has higher startup overhead; Hive better for very short jobs</t>
-  </si>
-  <si>
-    <t>CMP-005,SQL_Compatibility,HiveQL + ANSI SQL,SQL-92 with HiveQL extensions,Full HiveQL support with additional ANSI SQL features,HiveQL with some SQL limitations,Similar,Both,Both support HiveQL; Spark SQL has better ANSI SQL compliance</t>
-  </si>
-  <si>
-    <t>CMP-006,ACID_Transactions,Partial (Delta Lake),Full ACID support (Hive 3.0+),ACID via Delta Lake (external),Native ACID transaction support,Hive better,Hive,Traditional data warehouse workloads requiring ACID favor Hive</t>
-  </si>
-  <si>
-    <t>CMP-007,Schema_Evolution,Yes (with Delta Lake),Yes (native),Schema evolution with Delta Lake,Native schema evolution support,Similar,Both,Both support schema evolution with different implementations</t>
-  </si>
-  <si>
-    <t>CMP-008,Partitioning,Bucket + Partition,PARTITION BY + CLUSTER BY,Both partition and bucket support,Partition and bucketing support,Similar,Both,Both support partitioning for performance</t>
-  </si>
-  <si>
-    <t>CMP-009,Indexing,No native index,Yes (ORC indexes, Bitmap),No native indexing; relies on partitioning,Native index support (ORC indexes, Bloom filters),Hive better,Data warehousing requiring indexes</t>
-  </si>
-  <si>
-    <t>CMP-010,Data_Formats,Parquet, ORC, JSON, CSV,Parquet, ORC, Avro, JSON, CSV,All major formats supported,Broad format support,Similar,Both,Both support columnar formats (Parquet/ORC)</t>
-  </si>
-  <si>
-    <t>CMP-011,Compression,Snappy, Zstd, Gzip, LZO,Snappy, Zlib, Gzip, LZO,Both support multiple compression codecs,Similar,Both,Compression reduces storage and improves I/O</t>
-  </si>
-  <si>
-    <t>CMP-012,Cost_Model,TCO based on memory,Storage-based TCO,Memory-intensive (higher compute cost),Storage-optimized (lower compute cost),Hive cheaper for large storage,Storage-oriented workloads,Hive typically has lower TCO for storage-heavy workloads</t>
-  </si>
-  <si>
-    <t>CMP-013,Resource_Management,Dynamic allocation,Static allocation (YARN),Dynamic executor allocation based on load,Static container allocation,Spark more efficient,Spark SQL,Spark's dynamic allocation optimizes resource usage</t>
-  </si>
-  <si>
-    <t>CMP-014,Fault_Tolerance,Recomputation via lineage,Rerun tasks from disk,Lineage-based recomputation (RDDs),Re-run failed tasks from disk,Similar,Both,Both provide fault tolerance through different mechanisms</t>
-  </si>
-  <si>
-    <t>CMP-015,Integration_With_BI_Tools,JDBC/ODBC + Thrift,JDBC/ODBC + Thrift,Both provide JDBC/ODBC connectors,Thrift server for JDBC connections,Similar,Both,Business intelligence tools connect similarly to both</t>
-  </si>
-  <si>
-    <t>CMP-016,Learning_Curve,Moderate (Python/Scala/SQL),Low (SQL focused),Requires understanding of Spark concepts,SQL-focused with simpler setup,Hive easier,SQL analysts,SQL-only users find Hive easier to start</t>
-  </si>
-  <si>
-    <t>CMP-017,Streaming_Support,Native Structured Streaming,Limited (Spark Streaming via Hive on Spark),Native streaming engine,Streaming through integration,Spark significantly better,Real-time/streaming workloads,Spark SQL integrates with Structured Streaming</t>
-  </si>
-  <si>
-    <t>CMP-018,ML_Integration,Native MLlib,External (Spark ML, R, Python),Integrated machine learning library,Requires external tools,Spark better,ML workloads,Spark SQL works seamlessly with MLlib</t>
-  </si>
-  <si>
-    <t>CMP-019,Adoption_Trend,Growing rapidly,Declining (Spark adoption),Increasing adoption in modern data stacks,Traditional enterprise adoption,Spark SQL trending,New projects,Industry moving toward Spark SQL for performance</t>
-  </si>
-  <si>
-    <t>CMP-020,Community_Size,Large and growing,Large but stabilizing,Active open-source community,Mature enterprise community,Spark more active,Modern applications,Spark has more active development</t>
-  </si>
-  <si>
-    <t>CMP-021,Use_Case_Interactive_Analytics,Excellent,Good,Sub-second to seconds query response,Minutes to hours response,Spark better,BI dashboards, interactive queries,Spark SQL for low-latency analytics</t>
-  </si>
-  <si>
-    <t>CMP-022,Use_Case_Batch_ETL,Excellent (faster),Good (reliable),Fast ETL with memory processing,Reliable batch processing,Spark faster,Hive for stable ETL,Spark for speed; Hive for reliability in batch</t>
-  </si>
-  <si>
-    <t>CMP-023,Use_Case_Data_Warehousing,Good,Excellent,Mature warehouse features,Traditional data warehouse features,Hive better,Enterprise data warehouse,Hive has mature warehouse features</t>
-  </si>
-  <si>
-    <t>CMP-024,Use_Case_Real_Time,Excellent,Poor,Integrated with Structured Streaming,Limited streaming support,Spark better,Real-time analytics,Spark SQL for streaming applications</t>
-  </si>
-  <si>
-    <t>CMP-025,Use_Case_Ad_Hoc_Queries,Excellent,Good,Interactive query performance,Slow query response,Spark better,Data exploration,Spark SQL for ad-hoc analysis</t>
-  </si>
-  <si>
-    <t>CMP-026,Use_Case_Complex_Joins,Excellent (broadcast join),Good,Optimized join strategies,Map-side joins,Spark better,Multi-table analytics,Spark SQL's broadcast join optimizes small-large joins</t>
-  </si>
-  <si>
-    <t>CMP-027,Use_Case_Machine_Learning,Excellent,Fair,Integrated with MLlib,Requires external integration,Spark better,Predictive analytics,Spark SQL + MLlib for ML pipelines</t>
-  </si>
-  <si>
-    <t>CMP-028,Use_Case_Historical_Reporting,Good,Excellent,Good performance on recent data,Optimized for historical queries,Hive better,Time-series historical analysis,Hive's storage optimization benefits historical data</t>
-  </si>
-  <si>
-    <t>CMP-029,Use_Case_Small_Queries,Poor (overhead),Good (low overhead),Startup overhead significant,Faster for small queries,Hive better,Quick lookups, Hive for small, frequent queries</t>
-  </si>
-  <si>
-    <t>CMP-030,Use_Case_Large_Queries,Excellent,Good,Scales well with cluster size,Can handle massive data,Spark better,Big data processing,Both handle big data; Spark is faster</t>
-  </si>
-  <si>
-    <t>Q.No,Question,Comparison_Aspect,Analysis_Required,Expected_Answer,Key_Learning</t>
-  </si>
-  <si>
-    <t>1,"What are the main differences between Spark SQL and Hive? Compare execution engines and performance.","Execution Engine","Analyze CMP-001, CMP-002, CMP-003","Spark SQL uses in-memory DAG execution (10-100x faster); Hive uses disk-based MapReduce (minutes to hours). Spark 5-10x faster for most workloads","Spark's in-memory processing provides massive speed advantage over Hive's disk-based execution"</t>
-  </si>
-  <si>
-    <t>2,"How does query latency compare between Spark SQL and Hive? When would you choose each?","Query Latency","Analyze CMP-002, CMP-029","Spark SQL: sub-second to minutes (interactive); Hive: minutes to hours (batch). Choose Spark for interactive, Hive for scheduled batch","Spark SQL for ad-hoc queries; Hive for scheduled batch processing"</t>
-  </si>
-  <si>
-    <t>3,"What are the startup time differences? How does this impact use cases?","Startup Time","Analyze CMP-004","Spark: 5-30 sec startup overhead; Hive: 2-10 sec. Spark slower for short queries; Hive better for many small queries","Consider startup overhead when choosing for small, frequent queries"</t>
-  </si>
-  <si>
-    <t>4,"How do Spark SQL and Hive compare in SQL compatibility? Which has better ANSI SQL support?","SQL Compatibility","Analyze CMP-005","Both support HiveQL; Spark SQL has better ANSI SQL compliance with additional functions","Spark SQL is more SQL-standard compliant; Hive has some limitations"</t>
-  </si>
-  <si>
-    <t>5,"Which technology has better ACID transaction support? When is this important?","ACID Transactions","Analyze CMP-006","Hive 3.0+ has native ACID support; Spark SQL requires Delta Lake. Hive better for traditional data warehousing","Choose Hive for workloads requiring strict ACID compliance"</t>
-  </si>
-  <si>
-    <t>6,"How do partitioning and indexing compare between Spark SQL and Hive?","Partitioning &amp; Indexing","Analyze CMP-008, CMP-009","Both support partitioning; Hive has native indexing (ORC indexes, Bloom filters); Spark SQL relies on partitioning","Hive's indexing can improve query performance; Spark SQL requires good partitioning strategy"</t>
-  </si>
-  <si>
-    <t>7,"What data formats do both support? Which is most efficient?","Data Formats","Analyze CMP-010, CMP-011","Both support columnar formats (Parquet, ORC) with compression. Parquet is preferred for Spark, ORC for Hive","Use columnar formats for better performance in both engines"</t>
-  </si>
-  <si>
-    <t>8,"How does the cost model differ? When is Hive more cost-effective?","Cost Model","Analyze CMP-012","Spark: memory-intensive (higher compute cost); Hive: storage-optimized (lower TCO for storage-heavy). Hive cheaper for archival data","Spark's memory requirements increase cost; Hive better for cost-sensitive storage"</t>
-  </si>
-  <si>
-    <t>9,"How does resource management differ? Which is more efficient?","Resource Management","Analyze CMP-013","Spark: dynamic allocation adjusts executors; Hive: static allocation. Spark more efficient for variable workloads","Dynamic allocation helps Spark optimize resource usage"</t>
-  </si>
-  <si>
-    <t>10,"How do fault tolerance mechanisms compare?","Fault Tolerance","Analyze CMP-014","Spark: lineage-based recomputation; Hive: re-run failed tasks from disk. Both provide fault tolerance","Different approaches but both ensure job reliability"</t>
-  </si>
-  <si>
-    <t>11,"What are the integration capabilities with BI tools?","BI Integration","Analyze CMP-015","Both provide JDBC/ODBC connectors and Thrift servers for BI tool integration","Both can serve as backend for Tableau, Power BI, etc."</t>
-  </si>
-  <si>
-    <t>12,"Which has a steeper learning curve? Who is the target user?","Learning Curve","Analyze CMP-016","Hive: easier for SQL analysts; Spark SQL: requires understanding of Spark concepts, Python/Scala","Choose based on team skills: Hive for SQL experts, Spark SQL for data engineers"</t>
-  </si>
-  <si>
-    <t>13,"How does streaming support compare? When would this be critical?","Streaming Support","Analyze CMP-017","Spark: Native Structured Streaming; Hive: limited. Critical for real-time analytics","Spark SQL is the clear choice for streaming/real-time workloads"</t>
-  </si>
-  <si>
-    <t>14,"How does machine learning integration compare?","ML Integration","Analyze CMP-018","Spark: integrated MLlib; Hive: requires external tools. Spark better for ML pipelines","Spark SQL + MLlib enables end-to-end ML workflows"</t>
-  </si>
-  <si>
-    <t>15,"What are the adoption trends? Which is better for new projects?","Adoption Trends","Analyze CMP-019, CMP-020","Spark SQL adoption growing rapidly; Hive stable but declining. Spark recommended for new projects","Industry moving toward Spark SQL for modern data architectures"</t>
-  </si>
-  <si>
-    <t>16,"For interactive analytics and BI dashboards, which is better?","Use Case: Interactive","Analyze CMP-021","Spark SQL (sub-second to seconds); Hive (minutes). Spark SQL is better for BI dashboards","Spark SQL enables interactive exploration; Hive too slow for dashboards"</t>
-  </si>
-  <si>
-    <t>17,"For batch ETL workloads, how do they compare?","Use Case: Batch ETL","Analyze CMP-022","Spark: faster execution; Hive: more reliable. Choose Spark for speed, Hive for stability","Spark for time-sensitive ETL; Hive for reliable scheduled jobs"</t>
-  </si>
-  <si>
-    <t>18,"For traditional data warehousing, which is more suitable?","Use Case: Data Warehousing","Analyze CMP-023","Hive has mature warehouse features (ACID, indexing). Better for enterprise data warehouse","Hive remains strong for traditional data warehousing"</t>
-  </si>
-  <si>
-    <t>19,"For real-time analytics, which is the clear choice?","Use Case: Real-time","Analyze CMP-024","Spark SQL with Structured Streaming; Hive has poor streaming support. Spark is the clear choice","Spark SQL dominates for real-time analytics use cases"</t>
-  </si>
-  <si>
-    <t>20,"Create a decision framework for choosing between Spark SQL and Hive based on workload characteristics.","Decision Framework","Summarize all use cases","Interactive/Ad-hoc: Spark; Batch ETL: Spark for speed, Hive for stability; Data Warehouse: Hive; Real-time: Spark; Small queries: Hive; Large queries: Spark","Choose based on specific workload: latency, volume, complexity, team skills"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -199,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,285 +316,963 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Order_ID,Order_Date,Product_Name,Category,SubCategory,Sales_Amount,Quantity,Discount,Profit,Region,State,City,Payment_Method,Shipping_Mode,Customer_Segment,Priority,Return_Status,Satisfaction_Score</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1001,2024-01-05,MacBook Pro,Electronics,Computers,1299.99,1,0.05,389.99,North,Illinois,Chicago,Credit Card,Standard,Corporate,High,FALSE,4.8</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1002,2024-01-05,Magic Mouse,Electronics,Accessories,79.99,3,0.10,23.99,North,Illinois,Chicago,PayPal,Express,Corporate,Medium,FALSE,4.5</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1003,2024-01-06,Designer Jeans,Clothing,Mens,89.99,2,0.00,26.99,South,Texas,Houston,Debit Card,Standard,Consumer,Medium,FALSE,4.2</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1004,2024-01-06,27-inch Monitor,Electronics,Monitors,299.99,1,0.15,89.99,South,Texas,Austin,Credit Card,Express,Consumer,High,FALSE,4.9</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1005,2024-01-07,Executive Chair,Furniture,Chairs,399.99,2,0.05,119.99,East,New York,New York,Credit Card,Standard,Corporate,High,FALSE,5.0</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1006,2024-01-07,Mechanical Keyboard,Electronics,Keyboards,89.99,2,0.10,26.99,East,New York,Buffalo,PayPal,Standard,Consumer,Low,FALSE,3.5</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1007,2024-01-08,Leather Jacket,Clothing,Womens,199.99,1,0.20,59.99,West,California,Los Angeles,Debit Card,Express,Home Office,Medium,FALSE,4.7</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1008,2024-01-08,iPad,Electronics,Tablets,499.99,1,0.05,149.99,West,California,San Francisco,Credit Card,Standard,Corporate,High,FALSE,4.9</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1009,2024-01-09,Floor Lamp,Furniture,Lighting,79.99,2,0.00,23.99,North,Illinois,Chicago,PayPal,Standard,Consumer,Low,FALSE,4.0</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1010,2024-01-09,Running Shoes,Clothing,Mens,69.99,1,0.10,20.99,North,Michigan,Detroit,Debit Card,Express,Consumer,Medium,TRUE,2.8</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1011,2024-01-10,Gaming Laptop,Electronics,Computers,1299.99,1,0.15,389.99,South,Texas,Dallas,Credit Card,Standard,Corporate,High,FALSE,5.0</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1012,2024-01-10,Headphones,Electronics,Audio,149.99,2,0.05,44.99,East,Pennsylvania,Philadelphia,PayPal,Express,Consumer,Medium,FALSE,4.3</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1013,2024-01-11,Wool Coat,Clothing,Womens,189.99,1,0.20,56.99,West,California,San Diego,Debit Card,Standard,Home Office,Medium,FALSE,4.5</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1014,2024-01-11,Bookshelf,Furniture,Storage,159.99,1,0.10,47.99,North,Ohio,Columbus,Credit Card,Standard,Corporate,Medium,FALSE,4.2</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1015,2024-01-12,Smartphone,Electronics,Phones,699.99,2,0.05,209.99,South,Florida,Miami,Credit Card,Express,Consumer,High,FALSE,4.8</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1016,2024-01-12,Dress Shirt,Clothing,Mens,59.99,3,0.00,17.99,East,New York,New York,PayPal,Standard,Corporate,Medium,FALSE,4.4</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1017,2024-01-13,External SSD,Electronics,Storage,99.99,1,0.10,29.99,West,Oregon,Portland,Debit Card,Standard,Consumer,Low,FALSE,3.9</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1018,2024-01-13,Hoodie,Clothing,Womens,49.99,2,0.05,14.99,North,Illinois,Chicago,PayPal,Express,Consumer,Medium,TRUE,2.5</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1019,2024-01-14,Gaming Desk,Furniture,Desks,349.99,1,0.15,104.99,South,Texas,Austin,Credit Card,Standard,Corporate,High,FALSE,4.9</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1020,2024-01-14,Webcam,Electronics,Accessories,79.99,2,0.10,23.99,East,Massachusetts,Boston,PayPal,Express,Home Office,Medium,FALSE,4.6</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1021,2024-02-01,Docking Station,Electronics,Docks,129.99,1,0.00,38.99,West,Washington,Seattle,Debit Card,Standard,Consumer,Low,FALSE,4.1</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1022,2024-02-01,Winter Parka,Clothing,Mens,179.99,1,0.05,53.99,North,Minnesota,Minneapolis,Credit Card,Standard,Consumer,Medium,FALSE,4.3</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1023,2024-02-02,Office Desk,Furniture,Desks,449.99,1,0.10,134.99,South,Florida,Orlando,PayPal,Express,Corporate,High,FALSE,4.9</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1024,2024-02-02,USB-C Hub,Electronics,Cables,39.99,3,0.00,11.99,East,New Jersey,Newark,Debit Card,Standard,Consumer,Low,FALSE,3.8</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1025,2024-02-03,Casual Blazer,Clothing,Mens,149.99,1,0.15,44.99,West,California,Los Angeles,Credit Card,Express,Home Office,Medium,FALSE,4.7</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1026,2024-02-03,Gaming Mouse,Electronics,Accessories,59.99,2,0.10,17.99,North,Indiana,Indianapolis,PayPal,Standard,Consumer,Medium,TRUE,2.9</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1027,2024-02-04,Laser Printer,Electronics,Printers,199.99,1,0.05,59.99,South,Georgia,Atlanta,Debit Card,Standard,Corporate,High,FALSE,4.8</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1028,2024-02-04,Lounge Chair,Furniture,Chairs,279.99,1,0.20,83.99,East,Virginia,Richmond,Credit Card,Standard,Consumer,Medium,FALSE,4.2</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1029,2024-02-05,Power Bank,Electronics,Batteries,49.99,4,0.00,14.99,West,Arizona,Phoenix,PayPal,Express,Consumer,Low,FALSE,4.0</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1030,2024-02-05,Wool Scarf,Clothing,Accessories,24.99,5,0.10,7.49,North,Wisconsin,Milwaukee,Debit Card,Standard,Consumer,Medium,FALSE,4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1031,2024-02-06,Gaming Headset,Electronics,Audio,119.99,1,0.05,35.99,South,Texas,Houston,Credit Card,Express,Corporate,High,FALSE,4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1032,2024-02-06,Night Stand,Furniture,Storage,69.99,2,0.10,20.99,East,New York,Rochester,PayPal,Standard,Home Office,Medium,FALSE,4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1033,2024-02-07,Athletic Shoes,Clothing,Mens,109.99,1,0.15,32.99,West,California,San Jose,Debit Card,Standard,Consumer,Medium,FALSE,4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1034,2024-02-07,Smart Watch,Electronics,Wearables,199.99,1,0.05,59.99,North,Missouri,St Louis,Credit Card,Express,Consumer,High,FALSE,4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1035,2024-02-08,Bluetooth Speaker,Electronics,Audio,79.99,2,0.10,23.99,South,Florida,Tampa,PayPal,Standard,Corporate,Medium,FALSE,4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1036,2024-02-08,Cashmere Sweater,Clothing,Womens,99.99,1,0.00,29.99,East,Pennsylvania,Pittsburgh,Debit Card,Express,Consumer,Low,TRUE,2.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1037,2024-02-09,Bookshelf,Furniture,Storage,129.99,1,0.05,38.99,West,Oregon,Eugene,Credit Card,Standard,Home Office,Medium,FALSE,4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1038,2024-02-09,Mesh Router,Electronics,Networking,99.99,1,0.10,29.99,North,Iowa,Des Moines,PayPal,Standard,Consumer,Low,FALSE,4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1039,2024-02-10,Golf Polo,Clothing,Mens,44.99,3,0.15,13.49,South,Texas,San Antonio,Debit Card,Express,Consumer,Medium,FALSE,4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1040,2024-02-10,Graphics Card,Electronics,Components,499.99,1,0.20,149.99,West,Washington,Spokane,Credit Card,Standard,Corporate,High,FALSE,5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1041,2024-03-01,Desktop PC,Electronics,Computers,999.99,1,0.05,299.99,North,Illinois,Chicago,PayPal,Standard,Corporate,High,FALSE,4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1042,2024-03-01,Yoga Pants,Clothing,Womens,49.99,2,0.00,14.99,South,Texas,Austin,Debit Card,Express,Consumer,Medium,FALSE,4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1043,2024-03-02,Coffee Table,Furniture,Tables,249.99,1,0.10,74.99,East,New York,New York,Credit Card,Standard,Corporate,High,FALSE,4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1044,2024-03-02,Smart Speaker,Electronics,Smart Home,89.99,2,0.00,26.99,West,California,Los Angeles,PayPal,Express,Home Office,Medium,FALSE,4.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1045,2024-03-03,Baseball Cap,Clothing,Accessories,19.99,4,0.05,5.99,North,Michigan,Detroit,Debit Card,Standard,Consumer,Low,FALSE,3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1046,2024-03-03,Quadcopter,Electronics,Drones,349.99,1,0.10,104.99,South,Florida,Miami,Credit Card,Express,Consumer,High,FALSE,4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1047,2024-03-04,Wall Mirror,Furniture,Decor,59.99,2,0.00,17.99,East,Pennsylvania,Philadelphia,PayPal,Standard,Consumer,Medium,FALSE,4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1048,2024-03-04,Flannel Shirt,Clothing,Mens,49.99,2,0.10,14.99,West,Oregon,Portland,Debit Card,Standard,Home Office,Medium,FALSE,4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1049,2024-03-05,Streaming Stick,Electronics,Streaming,29.99,3,0.05,8.99,North,Ohio,Columbus,Credit Card,Standard,Consumer,Low,TRUE,2.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1050,2024-03-05,Leggings,Clothing,Womens,29.99,4,0.00,8.99,South,Georgia,Atlanta,PayPal,Express,Consumer,Medium,FALSE,4.3</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>31</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the CSV file 'Sales_Data.csv'. Load the data into Power BI. How many rows and columns are loaded after the initial connection?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the CSV file but use 'Transform Data' instead of 'Load'. Open Power Query Editor. What is the total number of rows and columns in the preview?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>When connecting to the CSV, change the delimiter from Comma to Semicolon. What happens to the data preview?</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Change the file encoding to 'UTF-8' when connecting. Then change to 'Windows 1252'. Does the preview show any differences?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>In the CSV connection dialog, check the 'Data Type Detection' options. Select 'Based on first 200 rows' vs 'Based on entire dataset'. How does this affect data type detection?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the CSV file and load it. Then go to Model View and check the data types of each column. Which columns were detected correctly? Which need manual correction?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the CSV file but specify that the file has no headers. How does the data appear? Then promote the first row to headers.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the CSV file and load only the first 10 rows for testing purposes. How many rows are loaded?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the CSV file and apply a filter in the connection dialog to only load orders from January 2024. How many rows are loaded?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the CSV file and change the data type of 'Order_Date' to Date during the connection process. Verify that dates are correctly parsed.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the CSV file but the file path contains spaces and special characters. How do you handle this?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a CSV file that is stored in a SharePoint folder. Use the SharePoint folder connector first, then select the CSV file.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a CSV file that is stored in OneDrive. Use the OneDrive connector to access the file.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a CSV file from a web URL (e.g., https://example.com/data.csv). Use the Web connector.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Connect to multiple CSV files in a folder (January.csv, February.csv, March.csv). Use the Folder connector and combine them.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>When combining multiple CSV files, select 'January.csv' as the sample file for transformations. Apply transformations to the sample, then see if they apply to all files.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a CSV file that uses comma as decimal separator and semicolon as field delimiter (European format). Configure the connection correctly.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a CSV file and use the 'Based on entire dataset' option for data type detection. Compare loading time with 'Based on first 200 rows'.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a CSV file that has 1 million rows. Use Query Folding techniques to filter data at the source if possible.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Connecting to a CSV File</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a parameter for the CSV file path. Then connect to the CSV using that parameter. This allows dynamic file switching.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>